--- a/data/nzd0097/nzd0097.xlsx
+++ b/data/nzd0097/nzd0097.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE273"/>
+  <dimension ref="A1:AE274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27451,6 +27451,105 @@
       <c r="AE273" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>395.11</v>
+      </c>
+      <c r="C274" t="n">
+        <v>404.22</v>
+      </c>
+      <c r="D274" t="n">
+        <v>383.45</v>
+      </c>
+      <c r="E274" t="n">
+        <v>361.71</v>
+      </c>
+      <c r="F274" t="n">
+        <v>359.63</v>
+      </c>
+      <c r="G274" t="n">
+        <v>361.93</v>
+      </c>
+      <c r="H274" t="n">
+        <v>366.22</v>
+      </c>
+      <c r="I274" t="n">
+        <v>373.88</v>
+      </c>
+      <c r="J274" t="n">
+        <v>377.07</v>
+      </c>
+      <c r="K274" t="n">
+        <v>381.91</v>
+      </c>
+      <c r="L274" t="n">
+        <v>386.81</v>
+      </c>
+      <c r="M274" t="n">
+        <v>393.39</v>
+      </c>
+      <c r="N274" t="n">
+        <v>391.46</v>
+      </c>
+      <c r="O274" t="n">
+        <v>387.66</v>
+      </c>
+      <c r="P274" t="n">
+        <v>392.35</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>395.03</v>
+      </c>
+      <c r="R274" t="n">
+        <v>392.52</v>
+      </c>
+      <c r="S274" t="n">
+        <v>389.84</v>
+      </c>
+      <c r="T274" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="U274" t="n">
+        <v>384.19</v>
+      </c>
+      <c r="V274" t="n">
+        <v>383.43</v>
+      </c>
+      <c r="W274" t="n">
+        <v>382.75</v>
+      </c>
+      <c r="X274" t="n">
+        <v>381.54</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>383.6</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>383.46</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>388.07</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>399.09</v>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -27465,7 +27564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B275"/>
+  <dimension ref="A1:B276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30218,6 +30317,16 @@
       </c>
       <c r="B275" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -30386,28 +30495,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09379981266043994</v>
+        <v>0.09560968969531627</v>
       </c>
       <c r="J2" t="n">
+        <v>273</v>
+      </c>
+      <c r="K2" t="n">
         <v>272</v>
       </c>
-      <c r="K2" t="n">
-        <v>271</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.0120937149534347</v>
+        <v>0.01265386077291375</v>
       </c>
       <c r="M2" t="n">
-        <v>4.381807360555191</v>
+        <v>4.374105170609944</v>
       </c>
       <c r="N2" t="n">
-        <v>38.10906823668865</v>
+        <v>37.99020229708444</v>
       </c>
       <c r="O2" t="n">
-        <v>6.173254266324096</v>
+        <v>6.163619253091842</v>
       </c>
       <c r="P2" t="n">
-        <v>390.1662905510377</v>
+        <v>390.1460475897409</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30468,28 +30577,28 @@
         <v>0.0609</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.02141398544444127</v>
+        <v>-0.01845671463930892</v>
       </c>
       <c r="J3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008021748903339621</v>
+        <v>0.0005997986551566914</v>
       </c>
       <c r="M3" t="n">
-        <v>4.360283285724553</v>
+        <v>4.358864607872986</v>
       </c>
       <c r="N3" t="n">
-        <v>30.23376547410342</v>
+        <v>30.17884521592302</v>
       </c>
       <c r="O3" t="n">
-        <v>5.498523935939846</v>
+        <v>5.493527574876003</v>
       </c>
       <c r="P3" t="n">
-        <v>400.8531199976707</v>
+        <v>400.8199655581477</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30546,28 +30655,28 @@
         <v>0.132</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.008847334245910584</v>
+        <v>-0.008209947902392633</v>
       </c>
       <c r="J4" t="n">
+        <v>273</v>
+      </c>
+      <c r="K4" t="n">
         <v>272</v>
       </c>
-      <c r="K4" t="n">
-        <v>271</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0002269402715611157</v>
+        <v>0.0001970019703922965</v>
       </c>
       <c r="M4" t="n">
-        <v>3.346315280501647</v>
+        <v>3.336994180486766</v>
       </c>
       <c r="N4" t="n">
-        <v>18.28212175901788</v>
+        <v>18.21754197753156</v>
       </c>
       <c r="O4" t="n">
-        <v>4.275759787338138</v>
+        <v>4.268201257852254</v>
       </c>
       <c r="P4" t="n">
-        <v>382.8381486360714</v>
+        <v>382.8310191079195</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30624,28 +30733,28 @@
         <v>0.1347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07306690851483706</v>
+        <v>0.06925099258548884</v>
       </c>
       <c r="J5" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K5" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01340178305355055</v>
+        <v>0.01209851625859215</v>
       </c>
       <c r="M5" t="n">
-        <v>3.526825910297564</v>
+        <v>3.532228491961207</v>
       </c>
       <c r="N5" t="n">
-        <v>20.87185739215819</v>
+        <v>20.88991270535867</v>
       </c>
       <c r="O5" t="n">
-        <v>4.56857279597887</v>
+        <v>4.57054840313049</v>
       </c>
       <c r="P5" t="n">
-        <v>364.8537075026475</v>
+        <v>364.8962910911765</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30702,28 +30811,28 @@
         <v>0.114</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2081254032169775</v>
+        <v>0.2037386884558807</v>
       </c>
       <c r="J6" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K6" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08476216320570562</v>
+        <v>0.0817511565039577</v>
       </c>
       <c r="M6" t="n">
-        <v>3.883046675778692</v>
+        <v>3.892500753207107</v>
       </c>
       <c r="N6" t="n">
-        <v>24.83842245734965</v>
+        <v>24.87233690716244</v>
       </c>
       <c r="O6" t="n">
-        <v>4.983816053723256</v>
+        <v>4.987217351104967</v>
       </c>
       <c r="P6" t="n">
-        <v>359.9019929553647</v>
+        <v>359.9509463547162</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30780,28 +30889,28 @@
         <v>0.1066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1652740724257346</v>
+        <v>0.1601960523601108</v>
       </c>
       <c r="J7" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K7" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06434522292505462</v>
+        <v>0.06070270160082336</v>
       </c>
       <c r="M7" t="n">
-        <v>3.624960259115056</v>
+        <v>3.638027199901601</v>
       </c>
       <c r="N7" t="n">
-        <v>21.09359858205609</v>
+        <v>21.18369756475649</v>
       </c>
       <c r="O7" t="n">
-        <v>4.592776783391077</v>
+        <v>4.602575101479224</v>
       </c>
       <c r="P7" t="n">
-        <v>364.27586243127</v>
+        <v>364.3325304294703</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30858,28 +30967,28 @@
         <v>0.1191</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04967460354807857</v>
+        <v>0.04503801151670464</v>
       </c>
       <c r="J8" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K8" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006035837341291983</v>
+        <v>0.004975489310764858</v>
       </c>
       <c r="M8" t="n">
-        <v>3.60848599597159</v>
+        <v>3.620502268234953</v>
       </c>
       <c r="N8" t="n">
-        <v>21.57962576092645</v>
+        <v>21.64011136389448</v>
       </c>
       <c r="O8" t="n">
-        <v>4.645387579193629</v>
+        <v>4.651893309599274</v>
       </c>
       <c r="P8" t="n">
-        <v>371.0953246697276</v>
+        <v>371.1470665662727</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30936,28 +31045,28 @@
         <v>0.1247</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05039403542287326</v>
+        <v>0.04793202392095251</v>
       </c>
       <c r="J9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K9" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006647808722335058</v>
+        <v>0.00605529861049392</v>
       </c>
       <c r="M9" t="n">
-        <v>3.434464657467335</v>
+        <v>3.435284389649453</v>
       </c>
       <c r="N9" t="n">
-        <v>20.15231317700295</v>
+        <v>20.1178371173393</v>
       </c>
       <c r="O9" t="n">
-        <v>4.489132786742107</v>
+        <v>4.485291196493188</v>
       </c>
       <c r="P9" t="n">
-        <v>375.8228431307323</v>
+        <v>375.8503178672549</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31014,28 +31123,28 @@
         <v>0.1072</v>
       </c>
       <c r="I10" t="n">
-        <v>0.117367821818911</v>
+        <v>0.1146426805950307</v>
       </c>
       <c r="J10" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K10" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02821206141493349</v>
+        <v>0.0271169285776125</v>
       </c>
       <c r="M10" t="n">
-        <v>3.763010052109825</v>
+        <v>3.762384911504018</v>
       </c>
       <c r="N10" t="n">
-        <v>25.19861459146508</v>
+        <v>25.15451270373131</v>
       </c>
       <c r="O10" t="n">
-        <v>5.019822167314802</v>
+        <v>5.015427469691025</v>
       </c>
       <c r="P10" t="n">
-        <v>377.5608802212782</v>
+        <v>377.591291345294</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31092,28 +31201,28 @@
         <v>0.1173</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1143111836322312</v>
+        <v>0.1131369915028925</v>
       </c>
       <c r="J11" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K11" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03468327503953583</v>
+        <v>0.03425298979077296</v>
       </c>
       <c r="M11" t="n">
-        <v>3.52115131329157</v>
+        <v>3.513243215525199</v>
       </c>
       <c r="N11" t="n">
-        <v>19.31385937340081</v>
+        <v>19.25206121148343</v>
       </c>
       <c r="O11" t="n">
-        <v>4.394753619191958</v>
+        <v>4.387717084257305</v>
       </c>
       <c r="P11" t="n">
-        <v>380.3976949821404</v>
+        <v>380.4107983406566</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31170,28 +31279,28 @@
         <v>0.1139</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07758684587022931</v>
+        <v>0.07863861764737115</v>
       </c>
       <c r="J12" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K12" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01524164040227949</v>
+        <v>0.01577235671078803</v>
       </c>
       <c r="M12" t="n">
-        <v>3.50152979723195</v>
+        <v>3.49344989664331</v>
       </c>
       <c r="N12" t="n">
-        <v>20.65456484809921</v>
+        <v>20.58608700499781</v>
       </c>
       <c r="O12" t="n">
-        <v>4.544729348167964</v>
+        <v>4.537189328758259</v>
       </c>
       <c r="P12" t="n">
-        <v>383.3101611290444</v>
+        <v>383.2984239164293</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31248,28 +31357,28 @@
         <v>0.1126</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08060397951431517</v>
+        <v>0.08353602329524418</v>
       </c>
       <c r="J13" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K13" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02071930517332576</v>
+        <v>0.02232357866897305</v>
       </c>
       <c r="M13" t="n">
-        <v>3.241970227275542</v>
+        <v>3.244099929351135</v>
       </c>
       <c r="N13" t="n">
-        <v>16.30748037530267</v>
+        <v>16.30354373952783</v>
       </c>
       <c r="O13" t="n">
-        <v>4.03825214360157</v>
+        <v>4.037764695908843</v>
       </c>
       <c r="P13" t="n">
-        <v>387.2895121315195</v>
+        <v>387.2567920852114</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31326,28 +31435,28 @@
         <v>0.1163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1507641580368632</v>
+        <v>0.1526211217708916</v>
       </c>
       <c r="J14" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K14" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05544458265082997</v>
+        <v>0.05712170710019537</v>
       </c>
       <c r="M14" t="n">
-        <v>3.572045141830831</v>
+        <v>3.567244239689662</v>
       </c>
       <c r="N14" t="n">
-        <v>20.56394475615564</v>
+        <v>20.51100010291692</v>
       </c>
       <c r="O14" t="n">
-        <v>4.534748587976585</v>
+        <v>4.528907164307623</v>
       </c>
       <c r="P14" t="n">
-        <v>384.9103686919096</v>
+        <v>384.8896459660878</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31404,28 +31513,28 @@
         <v>0.1195</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1952101986788828</v>
+        <v>0.1952699203849041</v>
       </c>
       <c r="J15" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K15" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L15" t="n">
-        <v>0.07296276813820834</v>
+        <v>0.07355999199712859</v>
       </c>
       <c r="M15" t="n">
-        <v>3.614129290202358</v>
+        <v>3.601138520468853</v>
       </c>
       <c r="N15" t="n">
-        <v>25.71240925590742</v>
+        <v>25.61824775603216</v>
       </c>
       <c r="O15" t="n">
-        <v>5.070740503704308</v>
+        <v>5.061447199767292</v>
       </c>
       <c r="P15" t="n">
-        <v>382.3222293253368</v>
+        <v>382.3215628629193</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31482,28 +31591,28 @@
         <v>0.1336</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1533871765813606</v>
+        <v>0.1565089911446481</v>
       </c>
       <c r="J16" t="n">
+        <v>273</v>
+      </c>
+      <c r="K16" t="n">
         <v>272</v>
       </c>
-      <c r="K16" t="n">
-        <v>271</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.07117410334807506</v>
+        <v>0.07417870024122131</v>
       </c>
       <c r="M16" t="n">
-        <v>3.287367202759771</v>
+        <v>3.292340963257808</v>
       </c>
       <c r="N16" t="n">
-        <v>16.28016438931214</v>
+        <v>16.28350684096923</v>
       </c>
       <c r="O16" t="n">
-        <v>4.034868571504175</v>
+        <v>4.035282746099612</v>
       </c>
       <c r="P16" t="n">
-        <v>384.0495145624524</v>
+        <v>384.0145979520074</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31560,28 +31669,28 @@
         <v>0.1213</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1262082057275946</v>
+        <v>0.1313381223648648</v>
       </c>
       <c r="J17" t="n">
+        <v>273</v>
+      </c>
+      <c r="K17" t="n">
         <v>272</v>
       </c>
-      <c r="K17" t="n">
-        <v>271</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.04749876746332171</v>
+        <v>0.05114535093043804</v>
       </c>
       <c r="M17" t="n">
-        <v>3.376587075438162</v>
+        <v>3.390139139916732</v>
       </c>
       <c r="N17" t="n">
-        <v>16.93441733930888</v>
+        <v>17.04277243779917</v>
       </c>
       <c r="O17" t="n">
-        <v>4.115144874644011</v>
+        <v>4.128289287077538</v>
       </c>
       <c r="P17" t="n">
-        <v>384.7783447977723</v>
+        <v>384.7209637674849</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31638,28 +31747,28 @@
         <v>0.1036</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1559585309438711</v>
+        <v>0.1605277184456717</v>
       </c>
       <c r="J18" t="n">
+        <v>273</v>
+      </c>
+      <c r="K18" t="n">
         <v>272</v>
       </c>
-      <c r="K18" t="n">
-        <v>271</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.08064724247416832</v>
+        <v>0.08495506112512508</v>
       </c>
       <c r="M18" t="n">
-        <v>3.015979456452339</v>
+        <v>3.026770102034573</v>
       </c>
       <c r="N18" t="n">
-        <v>14.70018497267535</v>
+        <v>14.78149444894493</v>
       </c>
       <c r="O18" t="n">
-        <v>3.834082024771424</v>
+        <v>3.844670915558955</v>
       </c>
       <c r="P18" t="n">
-        <v>382.2184076109666</v>
+        <v>382.1672986544341</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31716,28 +31825,28 @@
         <v>0.1031</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1971179368501108</v>
+        <v>0.1998643539847624</v>
       </c>
       <c r="J19" t="n">
+        <v>273</v>
+      </c>
+      <c r="K19" t="n">
         <v>272</v>
       </c>
-      <c r="K19" t="n">
-        <v>271</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1110625629067049</v>
+        <v>0.1143506513697276</v>
       </c>
       <c r="M19" t="n">
-        <v>3.156800943942394</v>
+        <v>3.161015977984628</v>
       </c>
       <c r="N19" t="n">
-        <v>16.48798800692341</v>
+        <v>16.4762724480814</v>
       </c>
       <c r="O19" t="n">
-        <v>4.060540358982214</v>
+        <v>4.059097491817782</v>
       </c>
       <c r="P19" t="n">
-        <v>380.8607524122822</v>
+        <v>380.8300321772515</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31794,28 +31903,28 @@
         <v>0.1098</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1839300686800049</v>
+        <v>0.1861008545073968</v>
       </c>
       <c r="J20" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K20" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L20" t="n">
-        <v>0.102024792490668</v>
+        <v>0.1047792837590318</v>
       </c>
       <c r="M20" t="n">
-        <v>3.10868769276549</v>
+        <v>3.107134818046072</v>
       </c>
       <c r="N20" t="n">
-        <v>15.8126982273149</v>
+        <v>15.78536133024439</v>
       </c>
       <c r="O20" t="n">
-        <v>3.976518354957626</v>
+        <v>3.973079577638031</v>
       </c>
       <c r="P20" t="n">
-        <v>377.655572397727</v>
+        <v>377.6313475845577</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31872,28 +31981,28 @@
         <v>0.0916</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1293497927309739</v>
+        <v>0.1316032712530446</v>
       </c>
       <c r="J21" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K21" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05387174734098055</v>
+        <v>0.05597957544392662</v>
       </c>
       <c r="M21" t="n">
-        <v>3.221404957066924</v>
+        <v>3.221378992057318</v>
       </c>
       <c r="N21" t="n">
-        <v>15.60494757817362</v>
+        <v>15.58074623605608</v>
       </c>
       <c r="O21" t="n">
-        <v>3.950309807872494</v>
+        <v>3.94724539850971</v>
       </c>
       <c r="P21" t="n">
-        <v>377.6877608848439</v>
+        <v>377.6626132652632</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31950,28 +32059,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1630783166756894</v>
+        <v>0.1647996426447831</v>
       </c>
       <c r="J22" t="n">
+        <v>273</v>
+      </c>
+      <c r="K22" t="n">
         <v>272</v>
       </c>
-      <c r="K22" t="n">
-        <v>271</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.06888974123105562</v>
+        <v>0.07072197564666627</v>
       </c>
       <c r="M22" t="n">
-        <v>3.48458955251594</v>
+        <v>3.481994085989772</v>
       </c>
       <c r="N22" t="n">
-        <v>18.88135878644748</v>
+        <v>18.83087318371067</v>
       </c>
       <c r="O22" t="n">
-        <v>4.345268551706267</v>
+        <v>4.339455401742328</v>
       </c>
       <c r="P22" t="n">
-        <v>376.7525938659549</v>
+        <v>376.7332426143535</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32028,28 +32137,28 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2623142243381797</v>
+        <v>0.2628374131237834</v>
       </c>
       <c r="J23" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K23" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1424771371560316</v>
+        <v>0.1439681135096699</v>
       </c>
       <c r="M23" t="n">
-        <v>3.752904492594625</v>
+        <v>3.741655287216651</v>
       </c>
       <c r="N23" t="n">
-        <v>21.5238129984218</v>
+        <v>21.44582112729149</v>
       </c>
       <c r="O23" t="n">
-        <v>4.639376358781619</v>
+        <v>4.630963304463931</v>
       </c>
       <c r="P23" t="n">
-        <v>374.9976453934837</v>
+        <v>374.991712591315</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32106,28 +32215,28 @@
         <v>0.0977</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3026750735574187</v>
+        <v>0.3014728871895084</v>
       </c>
       <c r="J24" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K24" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2269910797385745</v>
+        <v>0.2269498063947908</v>
       </c>
       <c r="M24" t="n">
-        <v>3.214450841105736</v>
+        <v>3.207760880224868</v>
       </c>
       <c r="N24" t="n">
-        <v>16.14880335755313</v>
+        <v>16.09824651108649</v>
       </c>
       <c r="O24" t="n">
-        <v>4.018557372684024</v>
+        <v>4.012262019246312</v>
       </c>
       <c r="P24" t="n">
-        <v>374.9572746185989</v>
+        <v>374.9709144975827</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -32184,28 +32293,28 @@
         <v>0.0916</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3172949854617784</v>
+        <v>0.317223197475084</v>
       </c>
       <c r="J25" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K25" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1679166151115408</v>
+        <v>0.1690137247175364</v>
       </c>
       <c r="M25" t="n">
-        <v>4.049241932257506</v>
+        <v>4.034629140345111</v>
       </c>
       <c r="N25" t="n">
-        <v>25.82325085693503</v>
+        <v>25.72799431788444</v>
       </c>
       <c r="O25" t="n">
-        <v>5.081658278252783</v>
+        <v>5.072277034812318</v>
       </c>
       <c r="P25" t="n">
-        <v>375.143419092126</v>
+        <v>375.1442335910066</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -32262,28 +32371,28 @@
         <v>0.1013</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1935931509796643</v>
+        <v>0.1963639279143624</v>
       </c>
       <c r="J26" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K26" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L26" t="n">
-        <v>0.07612205252697435</v>
+        <v>0.07859598961023917</v>
       </c>
       <c r="M26" t="n">
-        <v>3.765033520069148</v>
+        <v>3.765031929689849</v>
       </c>
       <c r="N26" t="n">
-        <v>23.54482171033568</v>
+        <v>23.50592302430017</v>
       </c>
       <c r="O26" t="n">
-        <v>4.852300661576494</v>
+        <v>4.848290732237514</v>
       </c>
       <c r="P26" t="n">
-        <v>373.1382665949045</v>
+        <v>373.1068296537702</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -32340,28 +32449,28 @@
         <v>0.1481</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2725303562752561</v>
+        <v>0.2754677229752555</v>
       </c>
       <c r="J27" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K27" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1040166095897158</v>
+        <v>0.1066641139663083</v>
       </c>
       <c r="M27" t="n">
-        <v>4.496963326430643</v>
+        <v>4.492599969242732</v>
       </c>
       <c r="N27" t="n">
-        <v>33.1160363769735</v>
+        <v>33.04776280060739</v>
       </c>
       <c r="O27" t="n">
-        <v>5.754653454116373</v>
+        <v>5.748718361566114</v>
       </c>
       <c r="P27" t="n">
-        <v>372.27640999303</v>
+        <v>372.243082942093</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -32418,28 +32527,28 @@
         <v>0.0771</v>
       </c>
       <c r="I28" t="n">
-        <v>0.277481915928186</v>
+        <v>0.2800917850370782</v>
       </c>
       <c r="J28" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K28" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L28" t="n">
-        <v>0.08410119102074509</v>
+        <v>0.08612961887028781</v>
       </c>
       <c r="M28" t="n">
-        <v>5.308314488295054</v>
+        <v>5.300492097156956</v>
       </c>
       <c r="N28" t="n">
-        <v>43.07235275374813</v>
+        <v>42.95495826825579</v>
       </c>
       <c r="O28" t="n">
-        <v>6.562953051313725</v>
+        <v>6.554003224614387</v>
       </c>
       <c r="P28" t="n">
-        <v>377.2056592911483</v>
+        <v>377.1758846235375</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -32496,28 +32605,28 @@
         <v>0.123</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2741962825216394</v>
+        <v>0.273671493166058</v>
       </c>
       <c r="J29" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K29" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1077033248608199</v>
+        <v>0.1081291266211616</v>
       </c>
       <c r="M29" t="n">
-        <v>4.523428913439862</v>
+        <v>4.509346408593777</v>
       </c>
       <c r="N29" t="n">
-        <v>31.99537223604035</v>
+        <v>31.87857439746843</v>
       </c>
       <c r="O29" t="n">
-        <v>5.656445194292997</v>
+        <v>5.646111440404663</v>
       </c>
       <c r="P29" t="n">
-        <v>388.7938878885697</v>
+        <v>388.7998749430833</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -32578,28 +32687,28 @@
         <v>0.1952</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01478414156644309</v>
+        <v>0.01581873834129239</v>
       </c>
       <c r="J30" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K30" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0002353157478451884</v>
+        <v>0.0002716393380414184</v>
       </c>
       <c r="M30" t="n">
-        <v>5.129690898154394</v>
+        <v>5.115537734133673</v>
       </c>
       <c r="N30" t="n">
-        <v>46.24701183427108</v>
+        <v>46.08076723937883</v>
       </c>
       <c r="O30" t="n">
-        <v>6.800515556505336</v>
+        <v>6.788281611673077</v>
       </c>
       <c r="P30" t="n">
-        <v>397.3867156798332</v>
+        <v>397.3746915993412</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -32641,7 +32750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE273"/>
+  <dimension ref="A1:AE274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75381,6 +75490,163 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>-35.6945386585393,174.51476616042444</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>-35.69525530033567,174.514957415046</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>-35.69598638985931,174.51481726975456</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>-35.696727483772754,174.51481921349546</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>-35.69743350389377,174.51504779948098</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-35.69812809533697,174.51532273444198</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>-35.69881727607372,174.51561862485994</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>-35.69949191207902,174.51596149476094</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>-35.70017061814966,174.51628580152632</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>-35.700845995374046,174.5166280205967</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>-35.701521185884445,174.51697086547273</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>-35.70218458992689,174.51732813434995</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>-35.702860425907275,174.51763968509383</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-35.703547750517245,174.51794151577266</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>-35.7042029210578,174.51832851332796</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>-35.70484883071906,174.5187119075987</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>-35.705498315881826,174.51909017875246</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>-35.7061429439289,174.51948640965446</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>-35.70678183738042,174.51990806785162</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>-35.707411730719734,174.52036165330972</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>-35.708038382662274,174.5208201906115</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>-35.70866201181325,174.52128437679033</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>-35.709286871065714,174.5217450120765</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>-35.70988333980653,174.52224025863617</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>-35.710463530784594,174.5227679248593</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>-35.71103327774773,174.52332876268412</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>-35.711584776559434,174.52391602300582</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>-35.712114885899105,174.52453256324156</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>-35.712662701786705,174.52512346770587</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0097/nzd0097.xlsx
+++ b/data/nzd0097/nzd0097.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE274"/>
+  <dimension ref="A1:AE275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27548,6 +27548,105 @@
         <v>399.09</v>
       </c>
       <c r="AE274" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>395.63</v>
+      </c>
+      <c r="C275" t="n">
+        <v>403.85</v>
+      </c>
+      <c r="D275" t="n">
+        <v>383.68</v>
+      </c>
+      <c r="E275" t="n">
+        <v>363.67</v>
+      </c>
+      <c r="F275" t="n">
+        <v>360.91</v>
+      </c>
+      <c r="G275" t="n">
+        <v>363.03</v>
+      </c>
+      <c r="H275" t="n">
+        <v>367.63</v>
+      </c>
+      <c r="I275" t="n">
+        <v>374.98</v>
+      </c>
+      <c r="J275" t="n">
+        <v>378.06</v>
+      </c>
+      <c r="K275" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="L275" t="n">
+        <v>387.51</v>
+      </c>
+      <c r="M275" t="n">
+        <v>393.47</v>
+      </c>
+      <c r="N275" t="n">
+        <v>391.94</v>
+      </c>
+      <c r="O275" t="n">
+        <v>388.61</v>
+      </c>
+      <c r="P275" t="n">
+        <v>393.68</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>396.14</v>
+      </c>
+      <c r="R275" t="n">
+        <v>393.28</v>
+      </c>
+      <c r="S275" t="n">
+        <v>390.32</v>
+      </c>
+      <c r="T275" t="n">
+        <v>386.11</v>
+      </c>
+      <c r="U275" t="n">
+        <v>384.8</v>
+      </c>
+      <c r="V275" t="n">
+        <v>384.38</v>
+      </c>
+      <c r="W275" t="n">
+        <v>382.75</v>
+      </c>
+      <c r="X275" t="n">
+        <v>381.54</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>383.6</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>383.46</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>388.07</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>399.09</v>
+      </c>
+      <c r="AE275" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27564,7 +27663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B276"/>
+  <dimension ref="A1:B277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30327,6 +30426,16 @@
       </c>
       <c r="B276" t="n">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -30495,28 +30604,28 @@
         <v>0.0566</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09560968969531627</v>
+        <v>0.09777365297470747</v>
       </c>
       <c r="J2" t="n">
+        <v>274</v>
+      </c>
+      <c r="K2" t="n">
         <v>273</v>
       </c>
-      <c r="K2" t="n">
-        <v>272</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.01265386077291375</v>
+        <v>0.01332213600434318</v>
       </c>
       <c r="M2" t="n">
-        <v>4.374105170609944</v>
+        <v>4.368017711213226</v>
       </c>
       <c r="N2" t="n">
-        <v>37.99020229708444</v>
+        <v>37.88152950639732</v>
       </c>
       <c r="O2" t="n">
-        <v>6.163619253091842</v>
+        <v>6.154797275816428</v>
       </c>
       <c r="P2" t="n">
-        <v>390.1460475897409</v>
+        <v>390.1217590913507</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30577,28 +30686,28 @@
         <v>0.0609</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01845671463930892</v>
+        <v>-0.01581641145020375</v>
       </c>
       <c r="J3" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K3" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005997986551566914</v>
+        <v>0.0004434850223805631</v>
       </c>
       <c r="M3" t="n">
-        <v>4.358864607872986</v>
+        <v>4.356239706302002</v>
       </c>
       <c r="N3" t="n">
-        <v>30.17884521592302</v>
+        <v>30.11322231210031</v>
       </c>
       <c r="O3" t="n">
-        <v>5.493527574876003</v>
+        <v>5.487551577169941</v>
       </c>
       <c r="P3" t="n">
-        <v>400.8199655581477</v>
+        <v>400.7902603171115</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30655,28 +30764,28 @@
         <v>0.132</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.008209947902392633</v>
+        <v>-0.007414662400810425</v>
       </c>
       <c r="J4" t="n">
+        <v>274</v>
+      </c>
+      <c r="K4" t="n">
         <v>273</v>
       </c>
-      <c r="K4" t="n">
-        <v>272</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0001970019703922965</v>
+        <v>0.0001619735481581674</v>
       </c>
       <c r="M4" t="n">
-        <v>3.336994180486766</v>
+        <v>3.328447001061668</v>
       </c>
       <c r="N4" t="n">
-        <v>18.21754197753156</v>
+        <v>18.15492783686976</v>
       </c>
       <c r="O4" t="n">
-        <v>4.268201257852254</v>
+        <v>4.260859987944894</v>
       </c>
       <c r="P4" t="n">
-        <v>382.8310191079195</v>
+        <v>382.8220920839828</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30733,28 +30842,28 @@
         <v>0.1347</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06925099258548884</v>
+        <v>0.06694704077744687</v>
       </c>
       <c r="J5" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K5" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01209851625859215</v>
+        <v>0.01138912343825194</v>
       </c>
       <c r="M5" t="n">
-        <v>3.532228491961207</v>
+        <v>3.530324110118468</v>
       </c>
       <c r="N5" t="n">
-        <v>20.88991270535867</v>
+        <v>20.84826282745335</v>
       </c>
       <c r="O5" t="n">
-        <v>4.57054840313049</v>
+        <v>4.56598979712541</v>
       </c>
       <c r="P5" t="n">
-        <v>364.8962910911765</v>
+        <v>364.9220922697949</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30811,28 +30920,28 @@
         <v>0.114</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2037386884558807</v>
+        <v>0.2003579560088228</v>
       </c>
       <c r="J6" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K6" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0817511565039577</v>
+        <v>0.07965345776798261</v>
       </c>
       <c r="M6" t="n">
-        <v>3.892500753207107</v>
+        <v>3.896336479570661</v>
       </c>
       <c r="N6" t="n">
-        <v>24.87233690716244</v>
+        <v>24.8560409682736</v>
       </c>
       <c r="O6" t="n">
-        <v>4.987217351104967</v>
+        <v>4.985583312740205</v>
       </c>
       <c r="P6" t="n">
-        <v>359.9509463547162</v>
+        <v>359.9888060362524</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30889,28 +30998,28 @@
         <v>0.1066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1601960523601108</v>
+        <v>0.1560091712787691</v>
       </c>
       <c r="J7" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K7" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06070270160082336</v>
+        <v>0.05790410540325963</v>
       </c>
       <c r="M7" t="n">
-        <v>3.638027199901601</v>
+        <v>3.64637469043864</v>
       </c>
       <c r="N7" t="n">
-        <v>21.18369756475649</v>
+        <v>21.22061832082968</v>
       </c>
       <c r="O7" t="n">
-        <v>4.602575101479224</v>
+        <v>4.606584235724957</v>
       </c>
       <c r="P7" t="n">
-        <v>364.3325304294703</v>
+        <v>364.379417897453</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30967,28 +31076,28 @@
         <v>0.1191</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04503801151670464</v>
+        <v>0.04151504041310247</v>
       </c>
       <c r="J8" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K8" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004975489310764858</v>
+        <v>0.00424948088602084</v>
       </c>
       <c r="M8" t="n">
-        <v>3.620502268234953</v>
+        <v>3.626785038278604</v>
       </c>
       <c r="N8" t="n">
-        <v>21.64011136389448</v>
+        <v>21.64201086825118</v>
       </c>
       <c r="O8" t="n">
-        <v>4.651893309599274</v>
+        <v>4.652097469771155</v>
       </c>
       <c r="P8" t="n">
-        <v>371.1470665662727</v>
+        <v>371.1865191305121</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31045,28 +31154,28 @@
         <v>0.1247</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04793202392095251</v>
+        <v>0.04631826756872921</v>
       </c>
       <c r="J9" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K9" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00605529861049392</v>
+        <v>0.005698151300568832</v>
       </c>
       <c r="M9" t="n">
-        <v>3.435284389649453</v>
+        <v>3.431432451395731</v>
       </c>
       <c r="N9" t="n">
-        <v>20.1178371173393</v>
+        <v>20.06138460414886</v>
       </c>
       <c r="O9" t="n">
-        <v>4.485291196493188</v>
+        <v>4.478993704410496</v>
       </c>
       <c r="P9" t="n">
-        <v>375.8503178672549</v>
+        <v>375.8683897799334</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31123,28 +31232,28 @@
         <v>0.1072</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1146426805950307</v>
+        <v>0.1126894910369221</v>
       </c>
       <c r="J10" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K10" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0271169285776125</v>
+        <v>0.02640928933074671</v>
       </c>
       <c r="M10" t="n">
-        <v>3.762384911504018</v>
+        <v>3.757969978781764</v>
       </c>
       <c r="N10" t="n">
-        <v>25.15451270373131</v>
+        <v>25.08756791137363</v>
       </c>
       <c r="O10" t="n">
-        <v>5.015427469691025</v>
+        <v>5.008749136398591</v>
       </c>
       <c r="P10" t="n">
-        <v>377.591291345294</v>
+        <v>377.6131644558722</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31201,28 +31310,28 @@
         <v>0.1173</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1131369915028925</v>
+        <v>0.1121551332950237</v>
       </c>
       <c r="J11" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K11" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03425298979077296</v>
+        <v>0.03393781549789399</v>
       </c>
       <c r="M11" t="n">
-        <v>3.513243215525199</v>
+        <v>3.50460991949826</v>
       </c>
       <c r="N11" t="n">
-        <v>19.25206121148343</v>
+        <v>19.1880803869123</v>
       </c>
       <c r="O11" t="n">
-        <v>4.387717084257305</v>
+        <v>4.380420115344224</v>
       </c>
       <c r="P11" t="n">
-        <v>380.4107983406566</v>
+        <v>380.4217938393084</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31279,28 +31388,28 @@
         <v>0.1139</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07863861764737115</v>
+        <v>0.08019225345185473</v>
       </c>
       <c r="J12" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K12" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01577235671078803</v>
+        <v>0.01651152996647842</v>
       </c>
       <c r="M12" t="n">
-        <v>3.49344989664331</v>
+        <v>3.487711342773339</v>
       </c>
       <c r="N12" t="n">
-        <v>20.58608700499781</v>
+        <v>20.52668464977717</v>
       </c>
       <c r="O12" t="n">
-        <v>4.537189328758259</v>
+        <v>4.530638437326154</v>
       </c>
       <c r="P12" t="n">
-        <v>383.2984239164293</v>
+        <v>383.2810252734718</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31357,28 +31466,28 @@
         <v>0.1126</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08353602329524418</v>
+        <v>0.08647865295365613</v>
       </c>
       <c r="J13" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K13" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02232357866897305</v>
+        <v>0.02399613558491986</v>
       </c>
       <c r="M13" t="n">
-        <v>3.244099929351135</v>
+        <v>3.246152495865352</v>
       </c>
       <c r="N13" t="n">
-        <v>16.30354373952783</v>
+        <v>16.30046830884264</v>
       </c>
       <c r="O13" t="n">
-        <v>4.037764695908843</v>
+        <v>4.037383844625457</v>
       </c>
       <c r="P13" t="n">
-        <v>387.2567920852114</v>
+        <v>387.2238385689272</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31435,28 +31544,28 @@
         <v>0.1163</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1526211217708916</v>
+        <v>0.1547992713562679</v>
       </c>
       <c r="J14" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K14" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05712170710019537</v>
+        <v>0.05903734199040978</v>
       </c>
       <c r="M14" t="n">
-        <v>3.567244239689662</v>
+        <v>3.563826750458415</v>
       </c>
       <c r="N14" t="n">
-        <v>20.51100010291692</v>
+        <v>20.46705875266623</v>
       </c>
       <c r="O14" t="n">
-        <v>4.528907164307623</v>
+        <v>4.524053354312505</v>
       </c>
       <c r="P14" t="n">
-        <v>384.8896459660878</v>
+        <v>384.8652536040976</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31513,28 +31622,28 @@
         <v>0.1195</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1952699203849041</v>
+        <v>0.1960242919755279</v>
       </c>
       <c r="J15" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K15" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L15" t="n">
-        <v>0.07355999199712859</v>
+        <v>0.07464100215801384</v>
       </c>
       <c r="M15" t="n">
-        <v>3.601138520468853</v>
+        <v>3.591110563952933</v>
       </c>
       <c r="N15" t="n">
-        <v>25.61824775603216</v>
+        <v>25.52845887060455</v>
       </c>
       <c r="O15" t="n">
-        <v>5.061447199767292</v>
+        <v>5.052569531496281</v>
       </c>
       <c r="P15" t="n">
-        <v>382.3215628629193</v>
+        <v>382.3131149101079</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31591,28 +31700,28 @@
         <v>0.1336</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1565089911446481</v>
+        <v>0.1605594336655367</v>
       </c>
       <c r="J16" t="n">
+        <v>274</v>
+      </c>
+      <c r="K16" t="n">
         <v>273</v>
       </c>
-      <c r="K16" t="n">
-        <v>272</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.07417870024122131</v>
+        <v>0.07788190756524838</v>
       </c>
       <c r="M16" t="n">
-        <v>3.292340963257808</v>
+        <v>3.302171974798178</v>
       </c>
       <c r="N16" t="n">
-        <v>16.28350684096923</v>
+        <v>16.33066685352768</v>
       </c>
       <c r="O16" t="n">
-        <v>4.035282746099612</v>
+        <v>4.041121979540791</v>
       </c>
       <c r="P16" t="n">
-        <v>384.0145979520074</v>
+        <v>383.9691354584497</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31669,28 +31778,28 @@
         <v>0.1213</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1313381223648648</v>
+        <v>0.1372040438785836</v>
       </c>
       <c r="J17" t="n">
+        <v>274</v>
+      </c>
+      <c r="K17" t="n">
         <v>273</v>
       </c>
-      <c r="K17" t="n">
-        <v>272</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.05114535093043804</v>
+        <v>0.05529897888148183</v>
       </c>
       <c r="M17" t="n">
-        <v>3.390139139916732</v>
+        <v>3.407085487489126</v>
       </c>
       <c r="N17" t="n">
-        <v>17.04277243779917</v>
+        <v>17.20431182250864</v>
       </c>
       <c r="O17" t="n">
-        <v>4.128289287077538</v>
+        <v>4.147808074454343</v>
       </c>
       <c r="P17" t="n">
-        <v>384.7209637674849</v>
+        <v>384.6551192102037</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31747,28 +31856,28 @@
         <v>0.1036</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1605277184456717</v>
+        <v>0.1655826491995447</v>
       </c>
       <c r="J18" t="n">
+        <v>274</v>
+      </c>
+      <c r="K18" t="n">
         <v>273</v>
       </c>
-      <c r="K18" t="n">
-        <v>272</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.08495506112512508</v>
+        <v>0.08965230583334871</v>
       </c>
       <c r="M18" t="n">
-        <v>3.026770102034573</v>
+        <v>3.039707019145159</v>
       </c>
       <c r="N18" t="n">
-        <v>14.78149444894493</v>
+        <v>14.89366890742165</v>
       </c>
       <c r="O18" t="n">
-        <v>3.844670915558955</v>
+        <v>3.859231647287015</v>
       </c>
       <c r="P18" t="n">
-        <v>382.1672986544341</v>
+        <v>382.1105574115114</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31825,28 +31934,28 @@
         <v>0.1031</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1998643539847624</v>
+        <v>0.2029121339529341</v>
       </c>
       <c r="J19" t="n">
+        <v>274</v>
+      </c>
+      <c r="K19" t="n">
         <v>273</v>
       </c>
-      <c r="K19" t="n">
-        <v>272</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.1143506513697276</v>
+        <v>0.1179202193583141</v>
       </c>
       <c r="M19" t="n">
-        <v>3.161015977984628</v>
+        <v>3.167492903232007</v>
       </c>
       <c r="N19" t="n">
-        <v>16.4762724480814</v>
+        <v>16.47638131260008</v>
       </c>
       <c r="O19" t="n">
-        <v>4.059097491817782</v>
+        <v>4.05911090173699</v>
       </c>
       <c r="P19" t="n">
-        <v>380.8300321772515</v>
+        <v>380.7958210610227</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31903,28 +32012,28 @@
         <v>0.1098</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1861008545073968</v>
+        <v>0.1886648810967732</v>
       </c>
       <c r="J20" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K20" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1047792837590318</v>
+        <v>0.1078996164456706</v>
       </c>
       <c r="M20" t="n">
-        <v>3.107134818046072</v>
+        <v>3.107417323244132</v>
       </c>
       <c r="N20" t="n">
-        <v>15.78536133024439</v>
+        <v>15.77059130155232</v>
       </c>
       <c r="O20" t="n">
-        <v>3.973079577638031</v>
+        <v>3.971220379373615</v>
       </c>
       <c r="P20" t="n">
-        <v>377.6313475845577</v>
+        <v>377.6026339162493</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31981,28 +32090,28 @@
         <v>0.0916</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1316032712530446</v>
+        <v>0.1342636222086041</v>
       </c>
       <c r="J21" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K21" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05597957544392662</v>
+        <v>0.05841945973868712</v>
       </c>
       <c r="M21" t="n">
-        <v>3.221378992057318</v>
+        <v>3.223522896069643</v>
       </c>
       <c r="N21" t="n">
-        <v>15.58074623605608</v>
+        <v>15.57000229194696</v>
       </c>
       <c r="O21" t="n">
-        <v>3.94724539850971</v>
+        <v>3.945884221812262</v>
       </c>
       <c r="P21" t="n">
-        <v>377.6626132652632</v>
+        <v>377.6328208928914</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32059,28 +32168,28 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1647996426447831</v>
+        <v>0.1671944451043395</v>
       </c>
       <c r="J22" t="n">
+        <v>274</v>
+      </c>
+      <c r="K22" t="n">
         <v>273</v>
       </c>
-      <c r="K22" t="n">
-        <v>272</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.07072197564666627</v>
+        <v>0.07306545990139501</v>
       </c>
       <c r="M22" t="n">
-        <v>3.481994085989772</v>
+        <v>3.483501350128821</v>
       </c>
       <c r="N22" t="n">
-        <v>18.83087318371067</v>
+        <v>18.79868589238838</v>
       </c>
       <c r="O22" t="n">
-        <v>4.339455401742328</v>
+        <v>4.335745136927259</v>
       </c>
       <c r="P22" t="n">
-        <v>376.7332426143535</v>
+        <v>376.7062263395106</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32137,28 +32246,28 @@
         <v>0.09669999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2628374131237834</v>
+        <v>0.2633349347462506</v>
       </c>
       <c r="J23" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K23" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1439681135096699</v>
+        <v>0.1454483282554764</v>
       </c>
       <c r="M23" t="n">
-        <v>3.741655287216651</v>
+        <v>3.730341497864193</v>
       </c>
       <c r="N23" t="n">
-        <v>21.44582112729149</v>
+        <v>21.36825220617367</v>
       </c>
       <c r="O23" t="n">
-        <v>4.630963304463931</v>
+        <v>4.622580686821342</v>
       </c>
       <c r="P23" t="n">
-        <v>374.991712591315</v>
+        <v>374.9860512747828</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32215,28 +32324,28 @@
         <v>0.0977</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3014728871895084</v>
+        <v>0.3002695083925193</v>
       </c>
       <c r="J24" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K24" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2269498063947908</v>
+        <v>0.2269014533742039</v>
       </c>
       <c r="M24" t="n">
-        <v>3.207760880224868</v>
+        <v>3.201076208969175</v>
       </c>
       <c r="N24" t="n">
-        <v>16.09824651108649</v>
+        <v>16.04814935364924</v>
       </c>
       <c r="O24" t="n">
-        <v>4.012262019246312</v>
+        <v>4.006014147959196</v>
       </c>
       <c r="P24" t="n">
-        <v>374.9709144975827</v>
+        <v>374.9846148467277</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -32293,28 +32402,28 @@
         <v>0.0916</v>
       </c>
       <c r="I25" t="n">
-        <v>0.317223197475084</v>
+        <v>0.3171313927503067</v>
       </c>
       <c r="J25" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K25" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1690137247175364</v>
+        <v>0.1700992260903256</v>
       </c>
       <c r="M25" t="n">
-        <v>4.034629140345111</v>
+        <v>4.02021176097325</v>
       </c>
       <c r="N25" t="n">
-        <v>25.72799431788444</v>
+        <v>25.63345899344048</v>
       </c>
       <c r="O25" t="n">
-        <v>5.072277034812318</v>
+        <v>5.062949633705681</v>
       </c>
       <c r="P25" t="n">
-        <v>375.1442335910066</v>
+        <v>375.1452787787611</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -32371,28 +32480,28 @@
         <v>0.1013</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1963639279143624</v>
+        <v>0.1990780477908988</v>
       </c>
       <c r="J26" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K26" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L26" t="n">
-        <v>0.07859598961023917</v>
+        <v>0.08107682982505382</v>
       </c>
       <c r="M26" t="n">
-        <v>3.765031929689849</v>
+        <v>3.764642247426732</v>
       </c>
       <c r="N26" t="n">
-        <v>23.50592302430017</v>
+        <v>23.46573177657372</v>
       </c>
       <c r="O26" t="n">
-        <v>4.848290732237514</v>
+        <v>4.844144070583957</v>
       </c>
       <c r="P26" t="n">
-        <v>373.1068296537702</v>
+        <v>373.0759296661496</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -32449,28 +32558,28 @@
         <v>0.1481</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2754677229752555</v>
+        <v>0.2783405402357098</v>
       </c>
       <c r="J27" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K27" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1066641139663083</v>
+        <v>0.1093098845308075</v>
       </c>
       <c r="M27" t="n">
-        <v>4.492599969242732</v>
+        <v>4.487898738765866</v>
       </c>
       <c r="N27" t="n">
-        <v>33.04776280060739</v>
+        <v>32.97805525451025</v>
       </c>
       <c r="O27" t="n">
-        <v>5.748718361566114</v>
+        <v>5.742652283963417</v>
       </c>
       <c r="P27" t="n">
-        <v>372.243082942093</v>
+        <v>372.2103762003783</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -32527,28 +32636,28 @@
         <v>0.0771</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2800917850370782</v>
+        <v>0.2826417195098716</v>
       </c>
       <c r="J28" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K28" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L28" t="n">
-        <v>0.08612961887028781</v>
+        <v>0.08815764828930994</v>
       </c>
       <c r="M28" t="n">
-        <v>5.300492097156956</v>
+        <v>5.29236326312463</v>
       </c>
       <c r="N28" t="n">
-        <v>42.95495826825579</v>
+        <v>42.83683583768423</v>
       </c>
       <c r="O28" t="n">
-        <v>6.554003224614387</v>
+        <v>6.544985549081391</v>
       </c>
       <c r="P28" t="n">
-        <v>377.1758846235375</v>
+        <v>377.1466941538175</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -32605,28 +32714,28 @@
         <v>0.123</v>
       </c>
       <c r="I29" t="n">
-        <v>0.273671493166058</v>
+        <v>0.2731366040195081</v>
       </c>
       <c r="J29" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K29" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L29" t="n">
-        <v>0.1081291266211616</v>
+        <v>0.1085487518682808</v>
       </c>
       <c r="M29" t="n">
-        <v>4.509346408593777</v>
+        <v>4.495404869560233</v>
       </c>
       <c r="N29" t="n">
-        <v>31.87857439746843</v>
+        <v>31.76271820039089</v>
       </c>
       <c r="O29" t="n">
-        <v>5.646111440404663</v>
+        <v>5.635842279587931</v>
       </c>
       <c r="P29" t="n">
-        <v>388.7998749430833</v>
+        <v>388.8059981064832</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -32687,28 +32796,28 @@
         <v>0.1952</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01581873834129239</v>
+        <v>0.01683570642754521</v>
       </c>
       <c r="J30" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K30" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0002716393380414184</v>
+        <v>0.0003102448024238091</v>
       </c>
       <c r="M30" t="n">
-        <v>5.115537734133673</v>
+        <v>5.10136677795297</v>
       </c>
       <c r="N30" t="n">
-        <v>46.08076723937883</v>
+        <v>45.91559407555632</v>
       </c>
       <c r="O30" t="n">
-        <v>6.788281611673077</v>
+        <v>6.776104638769706</v>
       </c>
       <c r="P30" t="n">
-        <v>397.3746915993412</v>
+        <v>397.3628330211338</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -32750,7 +32859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE274"/>
+  <dimension ref="A1:AE275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75647,6 +75756,163 @@
         </is>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>-35.69453813679148,174.51477187090072</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>-35.695255671585144,174.51495335178717</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>-35.69598598895315,174.51481976341202</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-35.69672251583235,174.51483999892022</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-35.69743017918373,174.51506134450767</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-35.69812523814489,174.515334374792</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-35.69881352595884,174.51563351301817</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>-35.69948875962283,174.5159730201867</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-35.70016763906867,174.51629611454325</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-35.70084527316743,174.51663052074056</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-35.70151907943302,174.51697815761278</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>-35.70218433182667,174.51732895989687</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>-35.70285875991573,174.51764458082727</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>-35.70354442514795,174.517951190885</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>-35.70419811957183,174.51834198178295</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>-35.70484444311297,174.5187229327222</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>-35.70549506620657,174.51909757307456</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>-35.70614075514532,174.51949098577035</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>-35.706779035625054,174.51991361036616</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>-35.707408833975585,174.52036738373926</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>-35.70803384754502,174.5208290969712</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>-35.70866201181325,174.52128437679033</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>-35.709286871065714,174.5217450120765</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>-35.70988333980653,174.52224025863617</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>-35.710463530784594,174.5227679248593</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>-35.71103327774773,174.52332876268412</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>-35.711584776559434,174.52391602300582</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>-35.712114885899105,174.52453256324156</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>-35.712662701786705,174.52512346770587</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
